--- a/excel_routes/route_AJF_CAI_threats.xlsx
+++ b/excel_routes/route_AJF_CAI_threats.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_260726_at_14.46\reports\excel_routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_270726_at_12.25\reports\excel_routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA31CD6-C195-49BE-97D1-97490993A867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27C919F1-DF76-446E-8592-9ABCFEC4D1BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12972" yWindow="348" windowWidth="10068" windowHeight="10284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="53">
   <si>
     <t>Date</t>
   </si>
@@ -69,21 +69,24 @@
     <t>Nile Air NP-120</t>
   </si>
   <si>
+    <t>MED</t>
+  </si>
+  <si>
+    <t>SAR</t>
+  </si>
+  <si>
+    <t>30-JUL-26</t>
+  </si>
+  <si>
+    <t>Nile Air NP-110</t>
+  </si>
+  <si>
+    <t>05-AUG-26</t>
+  </si>
+  <si>
     <t>LOW</t>
   </si>
   <si>
-    <t>SAR</t>
-  </si>
-  <si>
-    <t>30-JUL-26</t>
-  </si>
-  <si>
-    <t>Nile Air NP-110</t>
-  </si>
-  <si>
-    <t>05-AUG-26</t>
-  </si>
-  <si>
     <t>06-AUG-26</t>
   </si>
   <si>
@@ -172,9 +175,6 @@
   </si>
   <si>
     <t>19-NOV-26</t>
-  </si>
-  <si>
-    <t>MED</t>
   </si>
   <si>
     <t>21-NOV-26</t>
@@ -225,14 +225,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor rgb="FFD4EDDA"/>
+        <fgColor rgb="FFFFF3CD"/>
+        <bgColor rgb="FFFFF3CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3CD"/>
-        <bgColor rgb="FFFFF3CD"/>
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor rgb="FFD4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -580,7 +580,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -644,10 +644,10 @@
         <v>403</v>
       </c>
       <c r="E2" s="2">
-        <v>420</v>
+        <v>569</v>
       </c>
       <c r="F2" s="2">
-        <v>-17</v>
+        <v>-166</v>
       </c>
       <c r="G2" s="2">
         <v>40</v>
@@ -667,22 +667,22 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D3" s="2">
-        <v>468</v>
+        <v>403</v>
       </c>
       <c r="E3" s="2">
         <v>463</v>
       </c>
       <c r="F3" s="2">
-        <v>5</v>
+        <v>-60</v>
       </c>
       <c r="G3" s="2">
         <v>40</v>
@@ -702,22 +702,22 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D4" s="2">
         <v>403</v>
       </c>
       <c r="E4" s="2">
-        <v>420</v>
+        <v>463</v>
       </c>
       <c r="F4" s="2">
-        <v>-17</v>
+        <v>-60</v>
       </c>
       <c r="G4" s="2">
         <v>40</v>
@@ -737,13 +737,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D5" s="2">
         <v>403</v>
@@ -763,8 +763,8 @@
       <c r="I5" s="2">
         <v>-10</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>14</v>
+      <c r="J5" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>15</v>
@@ -778,7 +778,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D6" s="2">
         <v>403</v>
@@ -798,8 +798,8 @@
       <c r="I6" s="2">
         <v>-10</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>14</v>
+      <c r="J6" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>15</v>
@@ -813,7 +813,7 @@
         <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D7" s="2">
         <v>403</v>
@@ -833,8 +833,8 @@
       <c r="I7" s="2">
         <v>-10</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>14</v>
+      <c r="J7" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>15</v>
@@ -848,7 +848,7 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D8" s="2">
         <v>403</v>
@@ -868,8 +868,8 @@
       <c r="I8" s="2">
         <v>-10</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>14</v>
+      <c r="J8" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>15</v>
@@ -883,16 +883,16 @@
         <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D9" s="2">
-        <v>468</v>
+        <v>403</v>
       </c>
       <c r="E9" s="2">
         <v>420</v>
       </c>
       <c r="F9" s="2">
-        <v>48</v>
+        <v>-17</v>
       </c>
       <c r="G9" s="2">
         <v>40</v>
@@ -903,8 +903,8 @@
       <c r="I9" s="2">
         <v>-10</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>14</v>
+      <c r="J9" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>15</v>
@@ -918,7 +918,7 @@
         <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D10" s="2">
         <v>468</v>
@@ -938,8 +938,8 @@
       <c r="I10" s="2">
         <v>-10</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>14</v>
+      <c r="J10" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>15</v>
@@ -953,16 +953,16 @@
         <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D11" s="2">
         <v>468</v>
       </c>
       <c r="E11" s="2">
-        <v>463</v>
+        <v>420</v>
       </c>
       <c r="F11" s="2">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="G11" s="2">
         <v>40</v>
@@ -973,8 +973,8 @@
       <c r="I11" s="2">
         <v>-10</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>14</v>
+      <c r="J11" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>15</v>
@@ -988,28 +988,28 @@
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D12" s="2">
         <v>468</v>
       </c>
       <c r="E12" s="2">
-        <v>482</v>
+        <v>463</v>
       </c>
       <c r="F12" s="2">
-        <v>-14</v>
+        <v>5</v>
       </c>
       <c r="G12" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H12" s="2">
         <v>30</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>14</v>
+        <v>-10</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>15</v>
@@ -1023,7 +1023,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D13" s="2">
         <v>468</v>
@@ -1043,8 +1043,8 @@
       <c r="I13" s="2">
         <v>0</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>14</v>
+      <c r="J13" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>15</v>
@@ -1058,7 +1058,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D14" s="2">
         <v>468</v>
@@ -1078,8 +1078,8 @@
       <c r="I14" s="2">
         <v>0</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>14</v>
+      <c r="J14" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>15</v>
@@ -1093,7 +1093,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D15" s="2">
         <v>468</v>
@@ -1113,8 +1113,8 @@
       <c r="I15" s="2">
         <v>0</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>14</v>
+      <c r="J15" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>15</v>
@@ -1128,7 +1128,7 @@
         <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D16" s="2">
         <v>468</v>
@@ -1148,8 +1148,8 @@
       <c r="I16" s="2">
         <v>0</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>14</v>
+      <c r="J16" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>15</v>
@@ -1163,7 +1163,7 @@
         <v>12</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D17" s="2">
         <v>468</v>
@@ -1183,8 +1183,8 @@
       <c r="I17" s="2">
         <v>0</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>14</v>
+      <c r="J17" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>15</v>
@@ -1198,7 +1198,7 @@
         <v>12</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D18" s="2">
         <v>468</v>
@@ -1218,8 +1218,8 @@
       <c r="I18" s="2">
         <v>0</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>14</v>
+      <c r="J18" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>15</v>
@@ -1233,7 +1233,7 @@
         <v>12</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D19" s="2">
         <v>468</v>
@@ -1253,8 +1253,8 @@
       <c r="I19" s="2">
         <v>0</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>14</v>
+      <c r="J19" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>15</v>
@@ -1268,7 +1268,7 @@
         <v>12</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D20" s="2">
         <v>468</v>
@@ -1288,8 +1288,8 @@
       <c r="I20" s="2">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>14</v>
+      <c r="J20" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>15</v>
@@ -1303,16 +1303,16 @@
         <v>12</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D21" s="2">
-        <v>403</v>
+        <v>468</v>
       </c>
       <c r="E21" s="2">
-        <v>435</v>
+        <v>482</v>
       </c>
       <c r="F21" s="2">
-        <v>-32</v>
+        <v>-14</v>
       </c>
       <c r="G21" s="2">
         <v>30</v>
@@ -1323,8 +1323,8 @@
       <c r="I21" s="2">
         <v>0</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>14</v>
+      <c r="J21" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>15</v>
@@ -1338,7 +1338,7 @@
         <v>12</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D22" s="2">
         <v>403</v>
@@ -1358,8 +1358,8 @@
       <c r="I22" s="2">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>14</v>
+      <c r="J22" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>15</v>
@@ -1373,7 +1373,7 @@
         <v>12</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D23" s="2">
         <v>403</v>
@@ -1393,8 +1393,8 @@
       <c r="I23" s="2">
         <v>0</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>14</v>
+      <c r="J23" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>15</v>
@@ -1408,7 +1408,7 @@
         <v>12</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D24" s="2">
         <v>403</v>
@@ -1428,8 +1428,8 @@
       <c r="I24" s="2">
         <v>0</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>14</v>
+      <c r="J24" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>15</v>
@@ -1443,7 +1443,7 @@
         <v>12</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D25" s="2">
         <v>403</v>
@@ -1463,8 +1463,8 @@
       <c r="I25" s="2">
         <v>0</v>
       </c>
-      <c r="J25" s="3" t="s">
-        <v>14</v>
+      <c r="J25" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>15</v>
@@ -1478,7 +1478,7 @@
         <v>12</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D26" s="2">
         <v>403</v>
@@ -1498,8 +1498,8 @@
       <c r="I26" s="2">
         <v>0</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>14</v>
+      <c r="J26" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>15</v>
@@ -1513,7 +1513,7 @@
         <v>12</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D27" s="2">
         <v>403</v>
@@ -1533,8 +1533,8 @@
       <c r="I27" s="2">
         <v>0</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>14</v>
+      <c r="J27" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>15</v>
@@ -1548,7 +1548,7 @@
         <v>12</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D28" s="2">
         <v>403</v>
@@ -1568,8 +1568,8 @@
       <c r="I28" s="2">
         <v>0</v>
       </c>
-      <c r="J28" s="3" t="s">
-        <v>14</v>
+      <c r="J28" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>15</v>
@@ -1583,7 +1583,7 @@
         <v>12</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D29" s="2">
         <v>403</v>
@@ -1603,8 +1603,8 @@
       <c r="I29" s="2">
         <v>0</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>14</v>
+      <c r="J29" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>15</v>
@@ -1618,7 +1618,7 @@
         <v>12</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D30" s="2">
         <v>403</v>
@@ -1638,8 +1638,8 @@
       <c r="I30" s="2">
         <v>0</v>
       </c>
-      <c r="J30" s="3" t="s">
-        <v>14</v>
+      <c r="J30" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>15</v>
@@ -1653,7 +1653,7 @@
         <v>12</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D31" s="2">
         <v>403</v>
@@ -1673,8 +1673,8 @@
       <c r="I31" s="2">
         <v>0</v>
       </c>
-      <c r="J31" s="3" t="s">
-        <v>14</v>
+      <c r="J31" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>15</v>
@@ -1688,7 +1688,7 @@
         <v>12</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D32" s="2">
         <v>403</v>
@@ -1708,8 +1708,8 @@
       <c r="I32" s="2">
         <v>0</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>14</v>
+      <c r="J32" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>15</v>
@@ -1723,7 +1723,7 @@
         <v>12</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D33" s="2">
         <v>403</v>
@@ -1743,8 +1743,8 @@
       <c r="I33" s="2">
         <v>0</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>14</v>
+      <c r="J33" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>15</v>
@@ -1758,16 +1758,16 @@
         <v>12</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D34" s="2">
         <v>403</v>
       </c>
       <c r="E34" s="2">
-        <v>790</v>
+        <v>435</v>
       </c>
       <c r="F34" s="2">
-        <v>-387</v>
+        <v>-32</v>
       </c>
       <c r="G34" s="2">
         <v>30</v>
@@ -1779,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>15</v>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D35" s="2">
         <v>403</v>
@@ -1813,8 +1813,8 @@
       <c r="I35" s="2">
         <v>0</v>
       </c>
-      <c r="J35" s="4" t="s">
-        <v>49</v>
+      <c r="J35" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>15</v>
@@ -1822,22 +1822,22 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D36" s="2">
         <v>403</v>
       </c>
       <c r="E36" s="2">
-        <v>600</v>
+        <v>790</v>
       </c>
       <c r="F36" s="2">
-        <v>-197</v>
+        <v>-387</v>
       </c>
       <c r="G36" s="2">
         <v>30</v>
@@ -1857,13 +1857,13 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D37" s="2">
         <v>403</v>
@@ -1883,10 +1883,45 @@
       <c r="I37" s="2">
         <v>0</v>
       </c>
-      <c r="J37" s="3" t="s">
-        <v>14</v>
+      <c r="J37" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="K37" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" s="2">
+        <v>403</v>
+      </c>
+      <c r="E38" s="2">
+        <v>600</v>
+      </c>
+      <c r="F38" s="2">
+        <v>-197</v>
+      </c>
+      <c r="G38" s="2">
+        <v>30</v>
+      </c>
+      <c r="H38" s="2">
+        <v>30</v>
+      </c>
+      <c r="I38" s="2">
+        <v>0</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K38" s="2" t="s">
         <v>15</v>
       </c>
     </row>
